--- a/results/class_sensitivity/hsp90_leave_one_drug_out.xlsx
+++ b/results/class_sensitivity/hsp90_leave_one_drug_out.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,210 +446,267 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ALVESPIMYCIN</t>
+          <t>4-CHLOROPHENYLGUANIDINE</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2369562813639279</v>
+        <v>0.308174440338348</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2073944367486321</v>
+        <v>0.04437672162799396</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AT13387</t>
+          <t>ALVESPIMYCIN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
         <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3361512791991101</v>
+        <v>0.2483034835700878</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06933876905332938</v>
+        <v>0.1858163574155127</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BIIB021</t>
+          <t>AT13387</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2627363737486095</v>
+        <v>0.3286238756568276</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1607053923306587</v>
+        <v>0.07621517681278428</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GANETESPIB</t>
+          <t>BIIB021</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
         <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>0.327066416530492</v>
+        <v>0.3239514982778205</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0777013839759608</v>
+        <v>0.0807406130555955</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KW-2478</t>
+          <t>GANETESPIB</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3152091864980735</v>
+        <v>0.3470908910119507</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03950665006019696</v>
+        <v>0.0602153465452436</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NMS-E973</t>
+          <t>GUANIDINE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
         <v>43</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3513064531837657</v>
+        <v>0.3471530019960815</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02089042630924849</v>
+        <v>0.02256023208834077</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PU-H71</t>
+          <t>KW-2478</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
         <v>43</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3987917714841499</v>
+        <v>0.3167830867971992</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008075790244925243</v>
+        <v>0.03847916821274478</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SNX-5422</t>
+          <t>NMS-E973</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
         <v>43</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4377572238768447</v>
+        <v>0.3337235266970436</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003327851891859468</v>
+        <v>0.02874169551514223</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TANESPIMYCIN</t>
+          <t>PU-H71</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3139392610370912</v>
+        <v>0.3613502533285294</v>
       </c>
       <c r="E10" t="n">
-        <v>0.09112970018446108</v>
+        <v>0.01727625223105556</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VER-49009</t>
+          <t>SNX 2112</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
         <v>43</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3613366079438851</v>
+        <v>0.3568192156692376</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01728077864252696</v>
+        <v>0.0188353583650404</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>SNX-5422</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>13</v>
+      </c>
+      <c r="C12" t="n">
+        <v>43</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.3693214131525657</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.01479753869811546</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TANESPIMYCIN</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>13</v>
+      </c>
+      <c r="C13" t="n">
+        <v>30</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.2874624558893847</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1234842287577952</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>VER-49009</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="n">
+        <v>43</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.3355106685673316</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.02784590860131264</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>XL888</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>10</v>
-      </c>
-      <c r="C12" t="n">
-        <v>43</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.3290288513589139</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.03120922937461844</v>
+      <c r="B15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" t="n">
+        <v>43</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.3207219489835454</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.03600332098697278</v>
       </c>
     </row>
   </sheetData>

--- a/results/class_sensitivity/hsp90_leave_one_drug_out.xlsx
+++ b/results/class_sensitivity/hsp90_leave_one_drug_out.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,267 +446,229 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4-CHLOROPHENYLGUANIDINE</t>
+          <t>ALVESPIMYCIN</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>0.308174440338348</v>
+        <v>0.2435441326754003</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04437672162799396</v>
+        <v>0.1946671764001388</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ALVESPIMYCIN</t>
+          <t>AT13387</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
         <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2483034835700878</v>
+        <v>0.3165739710789767</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1858163574155127</v>
+        <v>0.08830235070547865</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AT13387</t>
+          <t>BIIB021</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3286238756568276</v>
+        <v>0.2780499284383684</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07621517681278428</v>
+        <v>0.136817593336162</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BIIB021</t>
+          <t>GANETESPIB</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
         <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3239514982778205</v>
+        <v>0.3146067435198066</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0807406130555955</v>
+        <v>0.09040699465200225</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GANETESPIB</t>
+          <t>KW-2478</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3470908910119507</v>
+        <v>0.3314704412545417</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0602153465452436</v>
+        <v>0.0299049443041285</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GUANIDINE</t>
+          <t>NMS-E973</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C7" t="n">
         <v>43</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3471530019960815</v>
+        <v>0.3470150724537035</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02256023208834077</v>
+        <v>0.02261754533515664</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KW-2478</t>
+          <t>PU-H71</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
         <v>43</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3167830867971992</v>
+        <v>0.3491919689427628</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03847916821274478</v>
+        <v>0.02172706541133545</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NMS-E973</t>
+          <t>SNX 2112</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
         <v>43</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3337235266970436</v>
+        <v>0.3482857614109044</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02874169551514223</v>
+        <v>0.02209412254134318</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PU-H71</t>
+          <t>SNX-5422</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
         <v>43</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3613502533285294</v>
+        <v>0.3584321517872078</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01727625223105556</v>
+        <v>0.01826730286316317</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SNX 2112</t>
+          <t>TANESPIMYCIN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3568192156692376</v>
+        <v>0.3079661847494773</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0188353583650404</v>
+        <v>0.09779374864678221</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SNX-5422</t>
+          <t>VER-49009</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
         <v>43</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3693214131525657</v>
+        <v>0.339840658550961</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01479753869811546</v>
+        <v>0.02577124734982442</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TANESPIMYCIN</t>
+          <t>XL888</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2874624558893847</v>
+        <v>0.3152210908426025</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1234842287577952</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>VER-49009</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>13</v>
-      </c>
-      <c r="C14" t="n">
-        <v>43</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.3355106685673316</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.02784590860131264</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>XL888</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>13</v>
-      </c>
-      <c r="C15" t="n">
-        <v>43</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.3207219489835454</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.03600332098697278</v>
+        <v>0.03949879529647581</v>
       </c>
     </row>
   </sheetData>
